--- a/public/downloads/project-tracker-gantt.xlsx
+++ b/public/downloads/project-tracker-gantt.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>Project tracker with Gantt</t>
   </si>
@@ -24,7 +24,7 @@
     <t>What this does</t>
   </si>
   <si>
-    <t>Tracks tasks, owners, dates and progress, and draws a Gantt chart from the dates without a single manual bar.</t>
+    <t>Tracks tasks, owners, dates and progress, and draws a Gantt chart from those dates without a single manual bar.</t>
   </si>
   <si>
     <t/>
@@ -33,31 +33,34 @@
     <t>Using it</t>
   </si>
   <si>
-    <t>1. Set the chart start date in cell N3 on the Tasks sheet. The timeline runs from there.</t>
-  </si>
-  <si>
-    <t>2. Enter each task with a start date, a duration in days, and an owner.</t>
-  </si>
-  <si>
-    <t>3. The End date and the Gantt bars calculate themselves.</t>
-  </si>
-  <si>
-    <t>4. Update Progress as work proceeds. The Status column follows it automatically.</t>
-  </si>
-  <si>
-    <t>How the Gantt works</t>
-  </si>
-  <si>
-    <t>There are no shapes and no drawing. Each timeline cell holds a conditional formatting rule that fills it when that day falls between the task start and end. Change a date and the chart redraws instantly.</t>
+    <t>1. Set the chart start date in the cream cell B3 on the Tasks sheet. The timeline runs from there.</t>
+  </si>
+  <si>
+    <t>2. Enter each task with an owner, a start date and a duration in days.</t>
+  </si>
+  <si>
+    <t>3. End date, Status and the chart bars all calculate themselves.</t>
+  </si>
+  <si>
+    <t>4. Update the Progress column as work proceeds.</t>
+  </si>
+  <si>
+    <t>How the chart works</t>
+  </si>
+  <si>
+    <t>There are no shapes and nothing is drawn. Each timeline cell carries a conditional formatting rule that fills it when its date falls between the task start and end. Change a date and the chart redraws instantly.</t>
+  </si>
+  <si>
+    <t>Completed tasks fill dark green, work in progress fills light green, and weekends are shaded so the working week stays readable.</t>
   </si>
   <si>
     <t>Extending the timeline</t>
   </si>
   <si>
-    <t>The timeline is 28 days wide. To cover longer projects, change the chart start date to move the window, or widen the block by copying the last timeline column to the right.</t>
-  </si>
-  <si>
-    <t>Cells with a white background are for you to fill in. Shaded cells hold formulas — changing one replaces the calculation with whatever you typed.</t>
+    <t>The timeline covers 42 days. Move the window by changing the start date, or widen it by copying the last timeline column to the right.</t>
+  </si>
+  <si>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
   </si>
   <si>
     <t>Project tracker</t>
@@ -162,7 +165,7 @@
     <t>Late</t>
   </si>
   <si>
-    <t>Started before today, no progress</t>
+    <t>Started before today with no progress</t>
   </si>
   <si>
     <t>Overall progress</t>
@@ -194,7 +197,7 @@
     <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
     <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -204,59 +207,64 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="15"/>
+      <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF0A4A3A"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF16324F"/>
+      <color rgb="FF141414"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF4A4A48"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,17 +273,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF0CE"/>
+        <fgColor rgb="FFE1F5EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16324F"/>
+        <fgColor rgb="FFFFFDF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F7F9"/>
+        <fgColor rgb="FF0F6E56"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -289,16 +302,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </left>
       <right style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </right>
       <top style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -306,52 +319,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,38 +378,43 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF2E7D5B"/>
+          <bgColor rgb="FF0F6E56"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF7FA8C4"/>
+          <bgColor rgb="FFC6E4D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEDF1F4"/>
+          <bgColor rgb="FFFAFAF8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FF2E7D5B"/>
+        <color rgb="FF0A4A3A"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE1F5EE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FFB4232B"/>
+        <color rgb="FF7A2020"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFAD5D3"/>
+          <bgColor rgb="FFF6DEDE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -731,17 +754,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF5A6B7B"/>
+    <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:B20"/>
+  <dimension ref="A2:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="96" customWidth="1"/>
+    <col min="2" max="2" width="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,88 +774,94 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+    <row r="6" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+    <row r="9" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+    <row r="16" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+    <row r="19" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="21" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -840,27 +869,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF16324F"/>
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="14" width="2" customWidth="1"/>
-    <col min="15" max="42" width="3.2" customWidth="1"/>
+    <col min="9" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -872,525 +900,665 @@
     </row>
     <row r="2" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="13:14" x14ac:dyDescent="0.25">
-      <c r="M3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="8">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="9">
         <v>46027</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="6" ht="26" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="10">
-        <f>$N$3+0</f>
-      </c>
-      <c r="P5" s="10">
-        <f>$N$3+1</f>
-      </c>
-      <c r="Q5" s="10">
-        <f>$N$3+2</f>
-      </c>
-      <c r="R5" s="10">
-        <f>$N$3+3</f>
-      </c>
-      <c r="S5" s="10">
-        <f>$N$3+4</f>
-      </c>
-      <c r="T5" s="10">
-        <f>$N$3+5</f>
-      </c>
-      <c r="U5" s="10">
-        <f>$N$3+6</f>
-      </c>
-      <c r="V5" s="10">
-        <f>$N$3+7</f>
-      </c>
-      <c r="W5" s="10">
-        <f>$N$3+8</f>
-      </c>
-      <c r="X5" s="10">
-        <f>$N$3+9</f>
-      </c>
-      <c r="Y5" s="10">
-        <f>$N$3+10</f>
-      </c>
-      <c r="Z5" s="10">
-        <f>$N$3+11</f>
-      </c>
-      <c r="AA5" s="10">
-        <f>$N$3+12</f>
-      </c>
-      <c r="AB5" s="10">
-        <f>$N$3+13</f>
-      </c>
-      <c r="AC5" s="10">
-        <f>$N$3+14</f>
-      </c>
-      <c r="AD5" s="10">
-        <f>$N$3+15</f>
-      </c>
-      <c r="AE5" s="10">
-        <f>$N$3+16</f>
-      </c>
-      <c r="AF5" s="10">
-        <f>$N$3+17</f>
-      </c>
-      <c r="AG5" s="10">
-        <f>$N$3+18</f>
-      </c>
-      <c r="AH5" s="10">
-        <f>$N$3+19</f>
-      </c>
-      <c r="AI5" s="10">
-        <f>$N$3+20</f>
-      </c>
-      <c r="AJ5" s="10">
-        <f>$N$3+21</f>
-      </c>
-      <c r="AK5" s="10">
-        <f>$N$3+22</f>
-      </c>
-      <c r="AL5" s="10">
-        <f>$N$3+23</f>
-      </c>
-      <c r="AM5" s="10">
-        <f>$N$3+24</f>
-      </c>
-      <c r="AN5" s="10">
-        <f>$N$3+25</f>
-      </c>
-      <c r="AO5" s="10">
-        <f>$N$3+26</f>
-      </c>
-      <c r="AP5" s="10">
-        <f>$N$3+27</f>
-      </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="H6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="11">
+        <f>$B$3+0</f>
+      </c>
+      <c r="J6" s="11">
+        <f>$B$3+1</f>
+      </c>
+      <c r="K6" s="11">
+        <f>$B$3+2</f>
+      </c>
+      <c r="L6" s="11">
+        <f>$B$3+3</f>
+      </c>
+      <c r="M6" s="11">
+        <f>$B$3+4</f>
+      </c>
+      <c r="N6" s="11">
+        <f>$B$3+5</f>
+      </c>
+      <c r="O6" s="11">
+        <f>$B$3+6</f>
+      </c>
+      <c r="P6" s="11">
+        <f>$B$3+7</f>
+      </c>
+      <c r="Q6" s="11">
+        <f>$B$3+8</f>
+      </c>
+      <c r="R6" s="11">
+        <f>$B$3+9</f>
+      </c>
+      <c r="S6" s="11">
+        <f>$B$3+10</f>
+      </c>
+      <c r="T6" s="11">
+        <f>$B$3+11</f>
+      </c>
+      <c r="U6" s="11">
+        <f>$B$3+12</f>
+      </c>
+      <c r="V6" s="11">
+        <f>$B$3+13</f>
+      </c>
+      <c r="W6" s="11">
+        <f>$B$3+14</f>
+      </c>
+      <c r="X6" s="11">
+        <f>$B$3+15</f>
+      </c>
+      <c r="Y6" s="11">
+        <f>$B$3+16</f>
+      </c>
+      <c r="Z6" s="11">
+        <f>$B$3+17</f>
+      </c>
+      <c r="AA6" s="11">
+        <f>$B$3+18</f>
+      </c>
+      <c r="AB6" s="11">
+        <f>$B$3+19</f>
+      </c>
+      <c r="AC6" s="11">
+        <f>$B$3+20</f>
+      </c>
+      <c r="AD6" s="11">
+        <f>$B$3+21</f>
+      </c>
+      <c r="AE6" s="11">
+        <f>$B$3+22</f>
+      </c>
+      <c r="AF6" s="11">
+        <f>$B$3+23</f>
+      </c>
+      <c r="AG6" s="11">
+        <f>$B$3+24</f>
+      </c>
+      <c r="AH6" s="11">
+        <f>$B$3+25</f>
+      </c>
+      <c r="AI6" s="11">
+        <f>$B$3+26</f>
+      </c>
+      <c r="AJ6" s="11">
+        <f>$B$3+27</f>
+      </c>
+      <c r="AK6" s="11">
+        <f>$B$3+28</f>
+      </c>
+      <c r="AL6" s="11">
+        <f>$B$3+29</f>
+      </c>
+      <c r="AM6" s="11">
+        <f>$B$3+30</f>
+      </c>
+      <c r="AN6" s="11">
+        <f>$B$3+31</f>
+      </c>
+      <c r="AO6" s="11">
+        <f>$B$3+32</f>
+      </c>
+      <c r="AP6" s="11">
+        <f>$B$3+33</f>
+      </c>
+      <c r="AQ6" s="11">
+        <f>$B$3+34</f>
+      </c>
+      <c r="AR6" s="11">
+        <f>$B$3+35</f>
+      </c>
+      <c r="AS6" s="11">
+        <f>$B$3+36</f>
+      </c>
+      <c r="AT6" s="11">
+        <f>$B$3+37</f>
+      </c>
+      <c r="AU6" s="11">
+        <f>$B$3+38</f>
+      </c>
+      <c r="AV6" s="11">
+        <f>$B$3+39</f>
+      </c>
+      <c r="AW6" s="11">
+        <f>$B$3+40</f>
+      </c>
+      <c r="AX6" s="11">
+        <f>$B$3+41</f>
+      </c>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
         <v>1</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="13">
+      <c r="C7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="14">
         <v>46027</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E7" s="15">
         <v>4</v>
       </c>
-      <c r="F6" s="13">
-        <f>IF(D6="","",D6+E6-1)</f>
-      </c>
-      <c r="G6" s="14">
+      <c r="F7" s="16">
+        <f>IF(OR(D7="",E7=""),"",D7+E7-1)</f>
+      </c>
+      <c r="G7" s="17">
         <v>1</v>
       </c>
-      <c r="H6" s="11">
-        <f>IF(G6=1,"Done",IF(G6&gt;0,"In progress",IF(D6&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="15"/>
-      <c r="Z6" s="15"/>
-      <c r="AA6" s="15"/>
-      <c r="AB6" s="15"/>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="15"/>
-      <c r="AE6" s="15"/>
-      <c r="AF6" s="15"/>
-      <c r="AG6" s="15"/>
-      <c r="AH6" s="15"/>
-      <c r="AI6" s="15"/>
-      <c r="AJ6" s="15"/>
-      <c r="AK6" s="15"/>
-      <c r="AL6" s="15"/>
-      <c r="AM6" s="15"/>
-      <c r="AN6" s="15"/>
-      <c r="AO6" s="15"/>
-      <c r="AP6" s="15"/>
-    </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="H7" s="12">
+        <f>IF(D7="","",IF(G7&gt;=1,"Done",IF(G7&gt;0,"In progress",IF(D7&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="18"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="18"/>
+      <c r="Z7" s="18"/>
+      <c r="AA7" s="18"/>
+      <c r="AB7" s="18"/>
+      <c r="AC7" s="18"/>
+      <c r="AD7" s="18"/>
+      <c r="AE7" s="18"/>
+      <c r="AF7" s="18"/>
+      <c r="AG7" s="18"/>
+      <c r="AH7" s="18"/>
+      <c r="AI7" s="18"/>
+      <c r="AJ7" s="18"/>
+      <c r="AK7" s="18"/>
+      <c r="AL7" s="18"/>
+      <c r="AM7" s="18"/>
+      <c r="AN7" s="18"/>
+      <c r="AO7" s="18"/>
+      <c r="AP7" s="18"/>
+      <c r="AQ7" s="18"/>
+      <c r="AR7" s="18"/>
+      <c r="AS7" s="18"/>
+      <c r="AT7" s="18"/>
+      <c r="AU7" s="18"/>
+      <c r="AV7" s="18"/>
+      <c r="AW7" s="18"/>
+      <c r="AX7" s="18"/>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>46031</v>
+      </c>
+      <c r="E8" s="15">
+        <v>3</v>
+      </c>
+      <c r="F8" s="20">
+        <f>IF(OR(D8="",E8=""),"",D8+E8-1)</f>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="19">
+        <f>IF(D8="","",IF(G8&gt;=1,"Done",IF(G8&gt;0,"In progress",IF(D8&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="18"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="18"/>
+      <c r="AG8" s="18"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="18"/>
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="18"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="18"/>
+      <c r="AQ8" s="18"/>
+      <c r="AR8" s="18"/>
+      <c r="AS8" s="18"/>
+      <c r="AT8" s="18"/>
+      <c r="AU8" s="18"/>
+      <c r="AV8" s="18"/>
+      <c r="AW8" s="18"/>
+      <c r="AX8" s="18"/>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="18">
-        <v>46031</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="D9" s="14">
+        <v>46034</v>
+      </c>
+      <c r="E9" s="15">
+        <v>6</v>
+      </c>
+      <c r="F9" s="16">
+        <f>IF(OR(D9="",E9=""),"",D9+E9-1)</f>
+      </c>
+      <c r="G9" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="H9" s="12">
+        <f>IF(D9="","",IF(G9&gt;=1,"Done",IF(G9&gt;0,"In progress",IF(D9&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="18"/>
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="18"/>
+      <c r="AG9" s="18"/>
+      <c r="AH9" s="18"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="18"/>
+      <c r="AN9" s="18"/>
+      <c r="AO9" s="18"/>
+      <c r="AP9" s="18"/>
+      <c r="AQ9" s="18"/>
+      <c r="AR9" s="18"/>
+      <c r="AS9" s="18"/>
+      <c r="AT9" s="18"/>
+      <c r="AU9" s="18"/>
+      <c r="AV9" s="18"/>
+      <c r="AW9" s="18"/>
+      <c r="AX9" s="18"/>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="14">
+        <v>46040</v>
+      </c>
+      <c r="E10" s="15">
+        <v>5</v>
+      </c>
+      <c r="F10" s="20">
+        <f>IF(OR(D10="",E10=""),"",D10+E10-1)</f>
+      </c>
+      <c r="G10" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="19">
+        <f>IF(D10="","",IF(G10&gt;=1,"Done",IF(G10&gt;0,"In progress",IF(D10&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="18"/>
+      <c r="X10" s="18"/>
+      <c r="Y10" s="18"/>
+      <c r="Z10" s="18"/>
+      <c r="AA10" s="18"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="18"/>
+      <c r="AE10" s="18"/>
+      <c r="AF10" s="18"/>
+      <c r="AG10" s="18"/>
+      <c r="AH10" s="18"/>
+      <c r="AI10" s="18"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="18"/>
+      <c r="AL10" s="18"/>
+      <c r="AM10" s="18"/>
+      <c r="AN10" s="18"/>
+      <c r="AO10" s="18"/>
+      <c r="AP10" s="18"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="18"/>
+      <c r="AS10" s="18"/>
+      <c r="AT10" s="18"/>
+      <c r="AU10" s="18"/>
+      <c r="AV10" s="18"/>
+      <c r="AW10" s="18"/>
+      <c r="AX10" s="18"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="14">
+        <v>46045</v>
+      </c>
+      <c r="E11" s="15">
+        <v>4</v>
+      </c>
+      <c r="F11" s="16">
+        <f>IF(OR(D11="",E11=""),"",D11+E11-1)</f>
+      </c>
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <f>IF(D11="","",IF(G11&gt;=1,"Done",IF(G11&gt;0,"In progress",IF(D11&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="18"/>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="18"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="18"/>
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="18"/>
+      <c r="AN11" s="18"/>
+      <c r="AO11" s="18"/>
+      <c r="AP11" s="18"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="18"/>
+      <c r="AS11" s="18"/>
+      <c r="AT11" s="18"/>
+      <c r="AU11" s="18"/>
+      <c r="AV11" s="18"/>
+      <c r="AW11" s="18"/>
+      <c r="AX11" s="18"/>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="14">
+        <v>46049</v>
+      </c>
+      <c r="E12" s="15">
         <v>3</v>
       </c>
-      <c r="F7" s="18">
-        <f>IF(D7="","",D7+E7-1)</f>
-      </c>
-      <c r="G7" s="19">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16">
-        <f>IF(G7=1,"Done",IF(G7&gt;0,"In progress",IF(D7&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="15"/>
-      <c r="AA7" s="15"/>
-      <c r="AB7" s="15"/>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="15"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="15"/>
-      <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
-      <c r="AL7" s="15"/>
-      <c r="AM7" s="15"/>
-      <c r="AN7" s="15"/>
-      <c r="AO7" s="15"/>
-      <c r="AP7" s="15"/>
-    </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>3</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="13">
-        <v>46034</v>
-      </c>
-      <c r="E8" s="11">
-        <v>6</v>
-      </c>
-      <c r="F8" s="13">
-        <f>IF(D8="","",D8+E8-1)</f>
-      </c>
-      <c r="G8" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="H8" s="11">
-        <f>IF(G8=1,"Done",IF(G8&gt;0,"In progress",IF(D8&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="15"/>
-      <c r="AL8" s="15"/>
-      <c r="AM8" s="15"/>
-      <c r="AN8" s="15"/>
-      <c r="AO8" s="15"/>
-      <c r="AP8" s="15"/>
-    </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
-        <v>4</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="18">
-        <v>46040</v>
-      </c>
-      <c r="E9" s="16">
-        <v>5</v>
-      </c>
-      <c r="F9" s="18">
-        <f>IF(D9="","",D9+E9-1)</f>
-      </c>
-      <c r="G9" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="16">
-        <f>IF(G9=1,"Done",IF(G9&gt;0,"In progress",IF(D9&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15"/>
-      <c r="AA9" s="15"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="15"/>
-      <c r="AI9" s="15"/>
-      <c r="AJ9" s="15"/>
-      <c r="AK9" s="15"/>
-      <c r="AL9" s="15"/>
-      <c r="AM9" s="15"/>
-      <c r="AN9" s="15"/>
-      <c r="AO9" s="15"/>
-      <c r="AP9" s="15"/>
-    </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>5</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="F12" s="20">
+        <f>IF(OR(D12="",E12=""),"",D12+E12-1)</f>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
+        <f>IF(D12="","",IF(G12&gt;=1,"Done",IF(G12&gt;0,"In progress",IF(D12&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="18"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="18"/>
+      <c r="AA12" s="18"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="18"/>
+      <c r="AF12" s="18"/>
+      <c r="AG12" s="18"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="18"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="18"/>
+      <c r="AM12" s="18"/>
+      <c r="AN12" s="18"/>
+      <c r="AO12" s="18"/>
+      <c r="AP12" s="18"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="18"/>
+      <c r="AS12" s="18"/>
+      <c r="AT12" s="18"/>
+      <c r="AU12" s="18"/>
+      <c r="AV12" s="18"/>
+      <c r="AW12" s="18"/>
+      <c r="AX12" s="18"/>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="13">
-        <v>46045</v>
-      </c>
-      <c r="E10" s="11">
-        <v>4</v>
-      </c>
-      <c r="F10" s="13">
-        <f>IF(D10="","",D10+E10-1)</f>
-      </c>
-      <c r="G10" s="14">
+      <c r="D13" s="14">
+        <v>46052</v>
+      </c>
+      <c r="E13" s="15">
+        <v>2</v>
+      </c>
+      <c r="F13" s="16">
+        <f>IF(OR(D13="",E13=""),"",D13+E13-1)</f>
+      </c>
+      <c r="G13" s="17">
         <v>0</v>
       </c>
-      <c r="H10" s="11">
-        <f>IF(G10=1,"Done",IF(G10&gt;0,"In progress",IF(D10&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="15"/>
-      <c r="AI10" s="15"/>
-      <c r="AJ10" s="15"/>
-      <c r="AK10" s="15"/>
-      <c r="AL10" s="15"/>
-      <c r="AM10" s="15"/>
-      <c r="AN10" s="15"/>
-      <c r="AO10" s="15"/>
-      <c r="AP10" s="15"/>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>6</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="18">
-        <v>46049</v>
-      </c>
-      <c r="E11" s="16">
-        <v>3</v>
-      </c>
-      <c r="F11" s="18">
-        <f>IF(D11="","",D11+E11-1)</f>
-      </c>
-      <c r="G11" s="19">
-        <v>0</v>
-      </c>
-      <c r="H11" s="16">
-        <f>IF(G11=1,"Done",IF(G11&gt;0,"In progress",IF(D11&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="15"/>
-      <c r="AB11" s="15"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="15"/>
-      <c r="AI11" s="15"/>
-      <c r="AJ11" s="15"/>
-      <c r="AK11" s="15"/>
-      <c r="AL11" s="15"/>
-      <c r="AM11" s="15"/>
-      <c r="AN11" s="15"/>
-      <c r="AO11" s="15"/>
-      <c r="AP11" s="15"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>7</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="13">
-        <v>46052</v>
-      </c>
-      <c r="E12" s="11">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13">
-        <f>IF(D12="","",D12+E12-1)</f>
-      </c>
-      <c r="G12" s="14">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <f>IF(G12=1,"Done",IF(G12&gt;0,"In progress",IF(D12&lt;TODAY(),"Late","Not started")))</f>
-      </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
-      <c r="AL12" s="15"/>
-      <c r="AM12" s="15"/>
-      <c r="AN12" s="15"/>
-      <c r="AO12" s="15"/>
-      <c r="AP12" s="15"/>
+      <c r="H13" s="12">
+        <f>IF(D13="","",IF(G13&gt;=1,"Done",IF(G13&gt;0,"In progress",IF(D13&lt;TODAY(),"Late","Not started"))))</f>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="18"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="18"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="18"/>
+      <c r="AL13" s="18"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="18"/>
+      <c r="AO13" s="18"/>
+      <c r="AP13" s="18"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="18"/>
+      <c r="AS13" s="18"/>
+      <c r="AT13" s="18"/>
+      <c r="AU13" s="18"/>
+      <c r="AV13" s="18"/>
+      <c r="AW13" s="18"/>
+      <c r="AX13" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O6:AP12">
+  <conditionalFormatting sqref="I7:AX13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(O$5&gt;=$D6,O$5&lt;=$F6,$G6=1)</formula>
+      <formula>AND($D7&lt;&gt;"",I$6&gt;=$D7,I$6&lt;=$F7,$G7&gt;=1)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(O$5&gt;=$D6,O$5&lt;=$F6)</formula>
+      <formula>AND($D7&lt;&gt;"",I$6&gt;=$D7,I$6&lt;=$F7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>WEEKDAY(O$5,2)&gt;5</formula>
+      <formula>WEEKDAY(I$6,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H12">
+  <conditionalFormatting sqref="H7:H13">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
@@ -1398,10 +1566,17 @@
       <formula>"Late"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Progress is a percentage" error="Enter a value between 0% and 100%." sqref="G7:G13">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1409,156 +1584,158 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF2E7D5B"/>
+    <tabColor rgb="FF0A4A3A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="12">
-        <f>COUNTA(Tasks!B6:B12)</f>
-      </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="21">
+        <f>COUNTA(Tasks!B7:B13)</f>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="17">
-        <f>COUNTIF(Tasks!H6:H12,"Done")</f>
-      </c>
-      <c r="C5" s="17" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="B6" s="22">
+        <f>COUNTIF(Tasks!H7:H13,"Done")</f>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="12">
-        <f>COUNTIF(Tasks!H6:H12,"In progress")</f>
-      </c>
-      <c r="C6" s="12" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="21">
+        <f>COUNTIF(Tasks!H7:H13,"In progress")</f>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="17">
-        <f>COUNTIF(Tasks!H6:H12,"Not started")</f>
-      </c>
-      <c r="C7" s="17" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="22">
+        <f>COUNTIF(Tasks!H7:H13,"Not started")</f>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="12">
-        <f>COUNTIF(Tasks!H6:H12,"Late")</f>
-      </c>
-      <c r="C8" s="12" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="21">
+        <f>COUNTIF(Tasks!H7:H13,"Late")</f>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="20">
-        <f>IFERROR(AVERAGE(Tasks!G6:G12),0)</f>
-      </c>
-      <c r="C9" s="17" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="23">
+        <f>IFERROR(AVERAGE(Tasks!G7:G13),0)</f>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="13">
-        <f>MIN(Tasks!D6:D12)</f>
-      </c>
-      <c r="C10" s="12" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="16">
+        <f>MIN(Tasks!D7:D13)</f>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="18">
-        <f>MAX(Tasks!F6:F12)</f>
-      </c>
-      <c r="C11" s="17" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="20">
+        <f>MAX(Tasks!F7:F13)</f>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="12">
-        <f>MAX(Tasks!F6:F12)-MIN(Tasks!D6:D12)+1</f>
-      </c>
-      <c r="C12" s="12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="21">
+        <f>MAX(Tasks!F7:F13)-MIN(Tasks!D7:D13)+1</f>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="17">
-        <f>NETWORKDAYS(MIN(Tasks!D6:D12),MAX(Tasks!F6:F12))</f>
-      </c>
-      <c r="C13" s="17" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
         <v>56</v>
       </c>
+      <c r="B14" s="22">
+        <f>NETWORKDAYS(MIN(Tasks!D7:D13),MAX(Tasks!F7:F13))</f>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/public/downloads/project-tracker-gantt.xlsx
+++ b/public/downloads/project-tracker-gantt.xlsx
@@ -60,7 +60,7 @@
     <t>The timeline covers 42 days. Move the window by changing the start date, or widen it by copying the last timeline column to the right.</t>
   </si>
   <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
   </si>
   <si>
     <t>Project tracker</t>
@@ -194,7 +194,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
@@ -859,7 +859,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1574,7 +1574,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1733,7 +1733,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/public/downloads/project-tracker-gantt.xlsx
+++ b/public/downloads/project-tracker-gantt.xlsx
@@ -744,33 +744,28 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -780,7 +775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -790,22 +785,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -815,12 +810,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
@@ -830,7 +825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
@@ -840,7 +835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
